--- a/data/Data.xlsx
+++ b/data/Data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Web Development\Indian Against India\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06EE9866-865F-49DF-9075-20FADE522E32}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB70E153-F9DB-4F76-AB73-986B30D1CB7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="119">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="140">
   <si>
     <t>Year</t>
   </si>
@@ -259,9 +259,6 @@
     <t>Congress, CPI(M), CPI, NC, PDP, TMC, DMK, AAP, SP, RJD, People's Union for Civil Liberties, Foreign-funded Activist NGOs</t>
   </si>
   <si>
-    <t>Congress, CPI(M), CPI, TMC, DMK, AAP, activist NGOs, Foreign-funded Activist NGOs</t>
-  </si>
-  <si>
     <t>Congress, CPI(M), CPI, TMC, AAP, DMK, RJD, SP, NCP, Shiv Sena (UBT), Foreign-funded Activist NGOs, Pseudo-Environmentalist</t>
   </si>
   <si>
@@ -394,6 +391,75 @@
   </si>
   <si>
     <t>https://www.indiatoday.in/news-analysis/story/a-tale-of-u-turns-on-the-three-farm-laws-1750146-2020-12-16</t>
+  </si>
+  <si>
+    <t>Kudankulam Nuclear Power Plant (Tamil Nadu)</t>
+  </si>
+  <si>
+    <t>Kudankulam is the beating heart of India’s energy security and strategic sovereignty. As India’s largest nuclear power station, it crushes our reliance on imported fossil fuels and hostile geopolitical energy blackmail. Generating gigawatts of unceasing, clean baseload power, it single-handedly fuels the massive industrial corridors of Southern India, powering defense manufacturing and high-tech infrastructure critical for national survival. It represents a monumental triumph of indigenous integration and strategic Indo-Russian partnership, built to survive the harshest extremes. In a world where energy starvation is weaponized to cripple sovereign nations, Kudankulam is an impregnable fortress of Atmanirbhar power—ensuring the Indian military-industrial complex and the economic engine of 1.4 billion citizens never go dark.</t>
+  </si>
+  <si>
+    <t>Congress, CPI(M), CPI, TMC, DMK, AAP,  Foreign-funded Activist NGOs</t>
+  </si>
+  <si>
+    <t>Anti-nuclear activists and foreign-funded NGOs flooded the Madras High Court and Supreme Court with PILs. Weaponizing the Fukushima disaster, they demanded a permanent halt to the project. They manufactured panic over environmental clearances, coastal regulation zone norms, nuclear liability, and disaster management, attempting to trap the critical strategic asset in endless judicial paralysis.</t>
+  </si>
+  <si>
+    <t>National security and scientific truth decimated the obstructionists. In May 2013, the Supreme Court unequivocally greenlit the project, ruling that nuclear energy is a vital sovereign necessity for economic growth and national security. Units 1 and 2 were successfully commissioned, and further reactors are rapidly advancing toward integration.</t>
+  </si>
+  <si>
+    <t>Vicious street blockades, orchestrated hunger strikes by the People's Movement Against Nuclear Energy (PMANE), and relentless legal sabotage halted construction and commissioning of Unit 1 for several critical years, pushing its grid synchronization from 2011 to 2013 and bleeding vast amounts of public funds.</t>
+  </si>
+  <si>
+    <t>The vicious campaign engineered by the Congress, the Left parties, DMK, and their INDI alliance ecosystem to choke the Kudankulam project was an egregious assault on India's national security and economic sovereignty. While foreign powers rapidly expanded their nuclear footprints to dominate the geopolitical energy grid, these regressive political outfits actively provided cover to foreign-funded NGOs and radical anarchists to paralyze a multi-billion-dollar strategic asset.
+By blockading the plant and fear-mongering among local populations, they deliberately starved Southern India of critical baseload electricity, crippling industrial output and causing thousands of crores in cost overruns for the national exchequer. Most unforgivably, their anti-development obstructionism directly compromised India's internal security. The then-Prime Minister Manmohan Singh himself admitted that foreign-funded NGOs were funneling dark money to stall the project, yet the broader opposition ecosystem unabashedly backed the agitators to score cheap vote-bank points.
+Every day Kudankulam was delayed, India was forced to rely on imported coal and foreign oil, bleeding foreign exchange and leaving our strategic defense manufacturing vulnerable to power deficits. Sacrificing India's self-reliance in advanced nuclear technology on the altar of foreign-funded activism and cynical electoral opportunism proves these opposition forces are fundamentally hostile to India's rise as an independent, unshakeable global superpower.</t>
+  </si>
+  <si>
+    <t>https://www.ndtv.com/india-news/kudankulam-protesters-getting-support-from-foreign-ngos-govt-498955</t>
+  </si>
+  <si>
+    <t>https://www.hindustantimes.com/delhi/3-ngos-diverted-foreign-funds-to-fuel-kudankulam-stir/story-iI1kYENA42b8JDolIrFkUI.html</t>
+  </si>
+  <si>
+    <t>https://www.businesstoday.in/industry/energy/story/sc-dismisses-plea-against-kudankulam-nuclear-power-plant-41070-2013-05-06</t>
+  </si>
+  <si>
+    <t>https://www.indiatoday.in/india/south/story/v-s-achuthanandan-stopped-from-visiting-kundankulam-116313-2012-09-17</t>
+  </si>
+  <si>
+    <t>POSCO $12 Billion Mega Steel Plant (Odisha)</t>
+  </si>
+  <si>
+    <t>The POSCO mega steel plant was an unprecedented $12 billion Foreign Direct Investment—the largest in India’s history at the time—designed to produce 12 million tonnes of high-grade steel annually. This was a monumental strategic asset for India's infrastructure and defense sovereignty. Domestic production of high-tensile steel is the backbone of naval shipbuilding, armored combat vehicles, and critical border infrastructure. Coupled with a captive deep-sea port at Jatadhar, this project was poised to shatter reliance on foreign supply chains, integrate India into global manufacturing networks, and permanently transform Odisha’s economy by creating tens of thousands of direct and indirect industrial jobs. It represented a crucial leap toward absolute self-reliance and geopolitical strength in strategic heavy manufacturing.</t>
+  </si>
+  <si>
+    <t>Congress, CPI(M), CPI, DMK, AAP, MDMK, PMANE, Foreign-Funded Activist NGOs, Pseudo-Environmentalist</t>
+  </si>
+  <si>
+    <t>Congress, CPI(M), CPI, POSCO Pratirodh Sangram Samiti (PPSS), Local Activist Groups, Foreign-Funded Activist NGOs</t>
+  </si>
+  <si>
+    <t>The project faced a relentless barrage of litigation before the National Green Tribunal (NGT), the Orissa High Court, and the Supreme Court. Opponents weaponized the Forest Rights Act (FRA) and Coastal Regulation Zone (CRZ) norms to file endless petitions, successfully forcing temporary suspensions of environmental clearances and trapping the land acquisition process in insurmountable judicial and bureaucratic gridlock.</t>
+  </si>
+  <si>
+    <t>After 12 years of extreme regulatory hurdles, violent ground protests, and shifting policies regarding captive iron ore mine allocations, POSCO officially withdrew from the project in 2017. The South Korean giant surrendered the acquired land, officially terminating India's largest-ever FDI initiative.</t>
+  </si>
+  <si>
+    <t>The project was completely paralyzed from the signing of the MoU in 2005 until its ultimate cancellation in 2017. Twelve years of land acquisition blockades, procedural delays, and legal injunctions prevented the massive manufacturing facility from ever being constructed.</t>
+  </si>
+  <si>
+    <t>The collapse of the POSCO mega steel plant stands as a colossal failure of India’s industrial ambitions and a severe, self-inflicted blow to its strategic economic sovereignty. While global competitors rapidly expanded their steel dominance and military-industrial capacities, India allowed a transformative $12 billion strategic investment to be systematically dismantled by endless protests, political obstructionism, and regulatory paralysis.
+By driving away this massive facility, India was deprived of 12 million tonnes of domestic high-grade steel production, which is absolutely essential for heavy infrastructure, rapid defense modernization, and naval expansion. The failure fractured global investor confidence, sending a damaging signal to international partners that critical infrastructure projects in India could be indefinitely stalled by political agitations and bureaucratic red tape. Furthermore, it robbed the state of Odisha of massive sovereign revenue and destroyed the prospect of tens of thousands of high-paying jobs for impoverished youth. The relentless opposition and subsequent withdrawal of POSCO severely hampered India's trajectory toward becoming a self-reliant global manufacturing superpower, forcing continued reliance on external supply chains and allowing hostile geopolitical rivals to maintain their dominance in strategic material production.</t>
+  </si>
+  <si>
+    <t>https://www.livemint.com/Companies/1r9u9TWe7q554c8xJFwwlM/Posco-said-to-be-backing-away-from-12-billion-India-project.html</t>
+  </si>
+  <si>
+    <t>https://economictimes.indiatimes.com/industry/indl-goods/svs/steel/south-koreas-posco-suspends-planned-12-bn-odisha-steel-project/articleshow/48101950.cms?from=mdr</t>
+  </si>
+  <si>
+    <t>https://www.business-humanrights.org/en/latest-news/india-amid-resistance-from-communities-posco-offers-to-surrender-land-acquired-for-12-billion-steel-project/</t>
   </si>
 </sst>
 </file>
@@ -514,8 +580,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{2DB3396E-FD0B-4F9C-842A-9832690A92E5}" name="Table2" displayName="Table2" ref="A1:L11" totalsRowShown="0" headerRowDxfId="13" dataDxfId="12">
-  <autoFilter ref="A1:L11" xr:uid="{2DB3396E-FD0B-4F9C-842A-9832690A92E5}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{2DB3396E-FD0B-4F9C-842A-9832690A92E5}" name="Table2" displayName="Table2" ref="A1:L13" totalsRowShown="0" headerRowDxfId="13" dataDxfId="12">
+  <autoFilter ref="A1:L13" xr:uid="{2DB3396E-FD0B-4F9C-842A-9832690A92E5}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:L11">
     <sortCondition ref="A1:A11"/>
   </sortState>
@@ -823,7 +889,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4B667CDE-8E2B-439F-AECC-B04A1264504F}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:L11"/>
+  <dimension ref="A1:L13"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="1"/>
@@ -957,37 +1023,37 @@
         <v>2016</v>
       </c>
       <c r="B4" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="C4" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="D4" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="E4" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="E4" s="2" t="s">
+      <c r="F4" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="F4" s="2" t="s">
+      <c r="G4" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="G4" s="2" t="s">
+      <c r="H4" s="2" t="s">
         <v>103</v>
       </c>
-      <c r="H4" s="2" t="s">
+      <c r="I4" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="I4" s="3" t="s">
+      <c r="J4" s="3" t="s">
         <v>105</v>
       </c>
-      <c r="J4" s="3" t="s">
+      <c r="K4" s="3" t="s">
         <v>106</v>
       </c>
-      <c r="K4" s="3" t="s">
+      <c r="L4" s="3" t="s">
         <v>107</v>
-      </c>
-      <c r="L4" s="3" t="s">
-        <v>108</v>
       </c>
     </row>
     <row r="5" spans="1:12" ht="409.5" x14ac:dyDescent="0.25">
@@ -1039,7 +1105,7 @@
         <v>41</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>42</v>
@@ -1077,7 +1143,7 @@
         <v>31</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>32</v>
@@ -1109,34 +1175,34 @@
         <v>2020</v>
       </c>
       <c r="B8" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="C8" s="2" t="s">
         <v>109</v>
       </c>
-      <c r="C8" s="2" t="s">
+      <c r="D8" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="D8" s="2" t="s">
+      <c r="E8" s="2" t="s">
         <v>111</v>
       </c>
-      <c r="E8" s="2" t="s">
+      <c r="F8" s="2" t="s">
         <v>112</v>
       </c>
-      <c r="F8" s="2" t="s">
+      <c r="G8" s="2" t="s">
         <v>113</v>
       </c>
-      <c r="G8" s="2" t="s">
+      <c r="H8" s="2" t="s">
         <v>114</v>
       </c>
-      <c r="H8" s="2" t="s">
+      <c r="I8" s="3" t="s">
         <v>115</v>
       </c>
-      <c r="I8" s="3" t="s">
+      <c r="J8" s="3" t="s">
         <v>116</v>
       </c>
-      <c r="J8" s="3" t="s">
+      <c r="K8" s="3" t="s">
         <v>117</v>
-      </c>
-      <c r="K8" s="3" t="s">
-        <v>118</v>
       </c>
       <c r="L8" s="2"/>
     </row>
@@ -1145,34 +1211,34 @@
         <v>2022</v>
       </c>
       <c r="B9" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="C9" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="C9" s="2" t="s">
+      <c r="D9" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="D9" s="2" t="s">
+      <c r="E9" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="E9" s="2" t="s">
+      <c r="F9" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="F9" s="2" t="s">
+      <c r="G9" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="G9" s="2" t="s">
+      <c r="H9" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="H9" s="2" t="s">
+      <c r="I9" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="I9" s="3" t="s">
+      <c r="J9" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="J9" s="3" t="s">
+      <c r="K9" s="3" t="s">
         <v>96</v>
-      </c>
-      <c r="K9" s="3" t="s">
-        <v>97</v>
       </c>
       <c r="L9" s="2"/>
     </row>
@@ -1181,37 +1247,37 @@
         <v>2024</v>
       </c>
       <c r="B10" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="C10" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="C10" s="2" t="s">
-        <v>77</v>
-      </c>
       <c r="D10" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="E10" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="E10" s="2" t="s">
+      <c r="F10" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="F10" s="2" t="s">
+      <c r="G10" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="G10" s="2" t="s">
+      <c r="H10" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="H10" s="2" t="s">
+      <c r="I10" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="J10" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="K10" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="L10" s="3" t="s">
         <v>83</v>
-      </c>
-      <c r="I10" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="J10" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="K10" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="L10" s="3" t="s">
-        <v>84</v>
       </c>
     </row>
     <row r="11" spans="1:12" ht="330" x14ac:dyDescent="0.25">
@@ -1225,7 +1291,7 @@
         <v>46</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>74</v>
+        <v>120</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>47</v>
@@ -1249,6 +1315,80 @@
         <v>26</v>
       </c>
       <c r="L11" s="2"/>
+    </row>
+    <row r="12" spans="1:12" ht="390" x14ac:dyDescent="0.25">
+      <c r="A12" s="2">
+        <v>2001</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="I12" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="J12" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="K12" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="L12" s="3" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" ht="345" x14ac:dyDescent="0.25">
+      <c r="A13" s="2">
+        <v>2005</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="I13" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="J13" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="K13" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="L13" s="2"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -1289,10 +1429,17 @@
     <hyperlink ref="I8" r:id="rId35" xr:uid="{927FA52B-EC13-4B9D-A3FD-27852A689C4B}"/>
     <hyperlink ref="J8" r:id="rId36" xr:uid="{5DD038AE-667D-4FA2-958D-B30E95434B80}"/>
     <hyperlink ref="K8" r:id="rId37" xr:uid="{43BF0A6D-76E3-484A-8993-305D643EA8F4}"/>
+    <hyperlink ref="I12" r:id="rId38" xr:uid="{0231CA09-72F3-4265-BE34-0B50995AF7B8}"/>
+    <hyperlink ref="J12" r:id="rId39" xr:uid="{E0679219-1095-4E52-A071-57264531CE9A}"/>
+    <hyperlink ref="K12" r:id="rId40" xr:uid="{32EE5611-1A29-45F6-B740-D210D9DF256F}"/>
+    <hyperlink ref="L12" r:id="rId41" xr:uid="{60061CF6-3F99-44AD-85D9-2D58C431A35E}"/>
+    <hyperlink ref="I13" r:id="rId42" xr:uid="{F201AD63-64AB-4E23-B1A2-A754D95D05BB}"/>
+    <hyperlink ref="J13" r:id="rId43" xr:uid="{C5EB7AEA-82C5-46D6-A06A-72D974C5ACD3}"/>
+    <hyperlink ref="K13" r:id="rId44" xr:uid="{0247CA60-0A5B-4BF2-9011-61F24CD43C64}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
-    <tablePart r:id="rId38"/>
+    <tablePart r:id="rId45"/>
   </tableParts>
 </worksheet>
 </file>
--- a/data/Data.xlsx
+++ b/data/Data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Web Development\Indian Against India\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB70E153-F9DB-4F76-AB73-986B30D1CB7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B9F4A543-C58E-489D-A8E8-CB4188F751E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="140">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="179" uniqueCount="179">
   <si>
     <t>Year</t>
   </si>
@@ -460,6 +460,129 @@
   </si>
   <si>
     <t>https://www.business-humanrights.org/en/latest-news/india-amid-resistance-from-communities-posco-offers-to-surrender-land-acquired-for-12-billion-steel-project/</t>
+  </si>
+  <si>
+    <t>Uniform Civil Code (UCC)</t>
+  </si>
+  <si>
+    <t>The Uniform Civil Code (UCC) is the ultimate constitutional weapon to forge an unbreakable, integrated, and sovereign India. A nation governed by a fractured patchwork of religious personal laws is inherently vulnerable to internal division, radicalization, and societal fragmentation. By establishing "One Nation, One Law," the UCC obliterates regressive practices like polygamy, halala, and discriminatory divorce that have brutally subjugated millions of women under the guise of religious autonomy. It replaces medieval orthodoxies with uncompromising constitutional equality, ensuring gender justice and equal inheritance rights for all citizens irrespective of faith.   Crucially, the UCC is a matter of profound national security and civilizational unity. It dismantles the toxic ecosystem of minority appeasement and vote-bank separatism that hostile elements exploit to divide Indian society. A unified legal framework ensures that loyalty to the Indian Constitution supersedes allegiance to clerical dictates and religious identity politics. It is the definitive step in realizing the vision of a truly secular republic, eradicating discriminatory parallel justice systems and binding 1.4 billion Indians under a single, unshakeable bedrock of modern civilizational law.</t>
+  </si>
+  <si>
+    <t>Congress, CPI(M), CPI, TMC, SP, RJD, AIMIM, DMK, AAP, All India Muslim Personal Law Board, Activist NGOs</t>
+  </si>
+  <si>
+    <t>Opponents, activist lobbies, and radical clerical boards repeatedly petitioned the Supreme Court, weaponizing the fundamental right to religious freedom (Article 25) and minority cultural rights (Article 29) to block a uniform code. They launched preemptive PILs against states like Uttarakhand, arguing that states lacked legislative competence, and falsely alleged the UCC was a ploy to impose majoritarian hegemony, aiming to trap the constitutional mandate of Article 44 in perpetual judicial limbo.</t>
+  </si>
+  <si>
+    <t>National integration and constitutional morality are decisively defeating appeasement. The Supreme Court has repeatedly rebuked the delay, echoing the absolute necessity of a UCC in landmark verdicts like Shah Bano and Sarla Mudgal. Breaking decades of political paralysis, Uttarakhand enacted independent India’s first comprehensive Uniform Civil Code, banning polygamy and standardizing marriage laws. States like Assam and Gujarat are rapidly advancing similar legislation, laying the undeniable groundwork for a mandatory nationwide code.</t>
+  </si>
+  <si>
+    <t>Paralyzed for over seven decades, the constitutional mandate of Article 44 was deliberately held hostage by successive Congress regimes. Pandering to orthodox clerics and radical vote banks, political establishments refused to draft a national code, famously reversing progressive judicial orders (such as the 1986 Muslim Women Act overturning the Shah Bano verdict) to appease fundamentalist outrage.</t>
+  </si>
+  <si>
+    <t>The criminal seven-decade delay in implementing the Uniform Civil Code is one of the most shameful betrayals of the Indian Constitution by the Congress, the Left parties, and their regressive INDI alliance ecosystem. By fiercely opposing a common civil framework, these obstructionist parties have actively sponsored and normalized gender apartheid in the world’s largest democracy. While hypocritically posturing as champions of liberalism, they deliberately fed millions of women to the wolves of medieval clerical orthodoxy—defending abhorrent, discriminatory practices like polygamy, halala, and unequal inheritance purely to secure captive block votes from fundamentalist clerics.
+Their venomous opposition to the UCC is a direct assault on national integration and internal security. By nurturing separate religious legal silos, the Congress and the Left have structurally incentivized radical separatism, allowing extremist networks to exploit these parallel justice systems to radicalize communities and challenge the sovereignty of the Indian state. Instead of forging a united national identity, the INDI alliance has treated religious minorities as political hostages, terrifying them with manufactured lies and fear-mongering campaigns claiming the UCC will erase their faith.
+Sacrificing the fundamental constitutional rights of women and the unshakeable unity of the Indian Republic to appease radical clerics exposes the complete moral bankruptcy of the opposition. Their fight to stall the Uniform Civil Code is not about protecting diversity; it is a treasonous effort to keep India fractured, divided, and perpetually chained to the dark ages of religious tribalism.</t>
+  </si>
+  <si>
+    <t>https://www.ndtv.com/india-news/left-congress-instilling-fear-among-minorities-on-ucc-uniform-minister-rajveev-chandrasekhar-4212137</t>
+  </si>
+  <si>
+    <t>https://indianexpress.com/article/india/minority-tribal-outfits-oppose-ucc-8862251/</t>
+  </si>
+  <si>
+    <t>Digital Personal Data Protection Act — 2023</t>
+  </si>
+  <si>
+    <t>The Digital Personal Data Protection (DPDP) Act establishes a comprehensive legal framework governing the processing of digital personal data in India. Proponents emphasize its critical role in asserting India's digital sovereignty and protecting the data of over a billion citizens from unregulated exploitation by multinational technology giants. From a national security perspective, the Act is viewed as an essential shield. It grants the government and its authorized agencies necessary exemptions to process data without explicit consent in the interest of sovereignty, integrity, and security of the state. Supporters argue this capability is vital for intelligence and law enforcement agencies to effectively counter cyber-terrorism, espionage, and digital radicalization, ensuring that data protection laws do not inadvertently paralyze the state's ability to defend its digital and physical borders.</t>
+  </si>
+  <si>
+    <t>Congress, CPI(M), CPI, TMC, AIMIM, Internet Freedom Foundation, Various Digital Rights NGOs</t>
+  </si>
+  <si>
+    <t>Digital rights activists and opposition lawmakers heavily scrutinized the draft bills, raising concerns that the broad exemptions granted to state agencies could lead to unchecked government surveillance. Critics cited the Supreme Court’s Puttaswamy judgment (Right to Privacy), arguing before parliamentary committees that the legislation lacked sufficient checks, balances, and independent oversight mechanisms to prevent potential misuse of citizen data by the state.</t>
+  </si>
+  <si>
+    <t>The Digital Personal Data Protection Bill was successfully passed by both houses of Parliament in August 2023. The enacted legislation established the Data Protection Board of India, defined protocols for cross-border data transfers, and retained the critical exemptions for government agencies necessary for maintaining national security and public order.</t>
+  </si>
+  <si>
+    <t>The legislative process experienced significant delays spanning five years. Following the initial 2018 draft, the subsequent 2019 Bill underwent extensive review by a Joint Parliamentary Committee. Amidst intense debates over the balance between individual privacy rights and state security requirements, the 2019 bill was withdrawn in 2022, delaying the final enactment until 2023.</t>
+  </si>
+  <si>
+    <t>Security analysts and proponents of the legislation argued that the five-year delay in enacting a robust data protection framework left a dangerous regulatory vacuum in India’s rapidly expanding digital ecosystem. During this prolonged legislative limbo, the personal, financial, and behavioral data of Indian citizens remained largely unprotected from aggressive data-mining practices by multinational tech corporations and potentially hostile foreign state actors. Without strict statutory guidelines and cross-border data transfer regulations, unregulated entities and foreign applications had prolonged windows to harvest domestic data, which could be exploited for psychological profiling, cyber-espionage, and coordinated misinformation campaigns.
+From a strategic standpoint, proponents maintain that prioritizing extensive debates over absolute privacy hindered the immediate establishment of a legal mechanism that empowers intelligence and law enforcement agencies. The delay prolonged the state's vulnerability, leaving India without a unified legal shield against digital colonization during a period marked by escalating global cyber-warfare. The absence of a definitive law regulating foreign tech platforms limited the government's ability to mandate rapid compliance and data localization, leaving critical digital infrastructure and citizen information exposed to unregulated international data flows for several crucial years.</t>
+  </si>
+  <si>
+    <t>https://www.thenewsminute.com/news/digital-personal-data-protection-bill-2023-what-are-opposition-s-main-objections-180288</t>
+  </si>
+  <si>
+    <t>http://theprint.in/politics/oppn-mps-walk-out-of-it-panel-meet-over-bid-to-push-data-protection-bill-before-it-reaches-parliament/1687145/</t>
+  </si>
+  <si>
+    <t>https://www.business-standard.com/india-news/india-bloc-demands-repeal-of-dpdp-section-44-to-save-rti-freedom-125041000917_1.html?utm_source=chatgpt.com</t>
+  </si>
+  <si>
+    <t>https://prsindia.org/billtrack/digital-personal-data-protection-bill-2023?utm</t>
+  </si>
+  <si>
+    <t>Right to Fair Compensation and Transparency in Land Acquisition, Rehabilitation and Resettlement (Amendment) Bill</t>
+  </si>
+  <si>
+    <t>The 2015 Amendment was a non-negotiable lifeline for India's strategic defense and rapid modernization. The draconian 2013 UPA law made it mathematically impossible to quickly acquire land for critical border infrastructure, military bases, and nuclear power plants due to agonizingly slow Social Impact Assessments (SIA) and impossible consent clauses. The 2015 amendment boldly exempted five critical pillars—including national security, defense production, and rural infrastructure—from these paralyzing bureaucratic hurdles. By fast-tracking land acquisition, it guaranteed that our armed forces wouldn't have to wait years for activist approvals just to build a forward operating base or border road against hostile adversaries like China and Pakistan. It was the ultimate catalyst for Atmanirbhar Bharat, unlocking sovereign wealth, industrializing rural India, and fortifying the nation's strategic defense corridors.</t>
+  </si>
+  <si>
+    <t>Congress, CPI(M), CPI, TMC, AAP, SP, JD(U), BKU, activist NGOs</t>
+  </si>
+  <si>
+    <t>Opponents and foreign-funded NGOs weaponized the judiciary, filing a barrage of writ petitions in the Supreme Court against the government's repeated promulgation of the Land Acquisition Ordinance. They argued it bypassed the legislative process, intentionally attempting to trigger a judicial freeze to paralyze land acquisition for strategic national projects and stall defense infrastructure indefinitely.</t>
+  </si>
+  <si>
+    <t>Sabotage succeeded at the central level. Lacking a majority in the Rajya Sabha and facing orchestrated political hostility and manufactured street protests, the government allowed the ordinance to lapse in August 2015. The central Bill was abandoned, and the Center advised individual states to frame their own amended land laws, decentralizing the reform.</t>
+  </si>
+  <si>
+    <t>Relentless parliamentary disruptions, hostile street agitations, and deliberate legislative gridlock completely killed the central reform. This forced critical national defense and infrastructure projects into years of catastrophic delay, as they were forced to navigate the draconian 2013 regulations until state governments could enact local bypasses.</t>
+  </si>
+  <si>
+    <t>The vicious murder of the 2015 Land Acquisition Amendment by the Congress, the Left parties, and their ideological ecosystem was a calculated stab in the back of India’s national security and economic sovereignty. By fighting ruthlessly to keep the paralyzing 2013 UPA law intact, this obstructionist syndicate effectively held the Indian Armed Forces hostage to bureaucratic red tape. Because of their sabotage, critical defense manufacturing hubs, forward military bases, and strategic border roads near the Line of Actual Control (LAC) were paralyzed for years, waiting for absurd "Social Impact Assessments" and forced consent from activist-backed lobbies.
+While hostile neighbors like China rapidly built militarized infrastructure on our borders, the Congress and the Left deliberately trapped India in domestic paralysis, proving they value manufactured political optics over sovereign territorial defense. Furthermore, they deliberately starved rural India of electrification, irrigation, and affordable housing, condemning millions to systemic poverty just to deny the government a legislative victory. Weaponizing farmer sentiments to block strategic land acquisition is a treasonous political gambit. Their victory in killing this bill delayed India’s rise as an industrial powerhouse by a decade, left strategic military supply lines vulnerable, and bled the national exchequer through astronomical cost overruns on stalled projects.</t>
+  </si>
+  <si>
+    <t>https://prsindia.org/billtrack/the-right-to-fair-compensation-and-transparency-in-land-acquisition-rehabilitation-and-resettlement-amendment-bill-2015</t>
+  </si>
+  <si>
+    <t>https://indianexpress.com/article/india/india-others/live-opposition-marches-against-land-acquisition-bill/</t>
+  </si>
+  <si>
+    <t>Goods and Services Tax (GST)</t>
+  </si>
+  <si>
+    <t>The Goods and Services Tax (GST) was introduced to replace a complex and fragmented structure of multiple central and state taxes with a unified national indirect tax system. Proponents emphasize that creating a "One Nation, One Tax" framework was essential for integrating the Indian market and removing domestic trade barriers. By dismantling state border checkposts, GST aimed to streamline logistics, ensuring that commercial and strategic cargo could move across the country more efficiently. Economically, the reform was designed to broaden the formal tax base, improve compliance, and reduce the cascading effect of taxes. Supporters argue that this financial formalization has been critical for increasing sovereign revenues, which in turn supports national infrastructure development and public expenditure. The unified tax system is viewed by policymakers as a vital step in modernizing India's economy and strengthening its fiscal capacity.</t>
+  </si>
+  <si>
+    <t>Congress, CPI(M), CPI, TMC, DMK, AAP</t>
+  </si>
+  <si>
+    <t>The GST rollout faced legal scrutiny regarding its constitutional validity, the federal structure, and the powers of the GST Council. Various petitions were filed in the Supreme Court and High Courts challenging aspects such as the Prevention of Anti-Profiteering provisions and the mechanisms for state compensation. These legal actions sought judicial review of the new tax framework to ensure it did not violate the financial autonomy of the states or constitutional provisions.</t>
+  </si>
+  <si>
+    <t>The 122nd Constitutional Amendment Bill was passed by Parliament, leading to the official rollout of the Goods and Services Tax during a midnight parliamentary session on July 1, 2017. The GST Council was established to oversee the tax rates and administrative framework, replacing the previous multi-tiered indirect tax system across the country.</t>
+  </si>
+  <si>
+    <t>The implementation of GST experienced a delay of over a decade from its initial conception. The legislative process was prolonged due to a lack of political consensus, with the opposition raising concerns over the revenue-sharing model, the proposed tax cap rates, and the dispute resolution mechanism, which led to parliamentary disruptions and a stalled passage in the Rajya Sabha.</t>
+  </si>
+  <si>
+    <t>Economic analysts who advocated for the swift implementation of the Goods and Services Tax argue that the decade-long delay prolonged structural inefficiencies within the Indian economy. During the years the legislation was stalled in Parliament, businesses were forced to continue navigating a highly fragmented tax environment characterized by overlapping central and state levies. This complex system often resulted in the cascading of taxes—where tax was paid on tax—which inflated operational costs for manufacturers and increased final prices for consumers.
+Proponents of the reform emphasize that the persistence of state border checkposts and varied state-level entry taxes during this delay caused significant logistical bottlenecks. The fragmented state policies increased transit times for commercial freight, disrupting supply chains and hindering the efficient movement of goods across the country, which impacted overall economic productivity.
+Furthermore, the delay is cited by supporters as having allowed a large portion of the unorganized sector to continue operating outside the formal tax net for an extended period, thereby depriving the national and state exchequers of substantial potential tax revenues. Advocates of the GST maintain that achieving a political consensus earlier would have accelerated the financial formalization of the economy, improved the ease of doing business for domestic and international investors sooner, and provided the government with increased, consolidated fiscal resources that could have been allocated toward public infrastructure and national development during the years the legislation remained stalled.</t>
+  </si>
+  <si>
+    <t>https://prsindia.org/billtrack/the-constitution-122nd-amendment-gst-bill-2014</t>
+  </si>
+  <si>
+    <t>https://indianexpress.com/article/political-pulse/amid-protests-gst-bill-tabled-in-rajya-sabha-angry-jaitley-slams-congress/?ref=archive_pg</t>
+  </si>
+  <si>
+    <t>https://blog.saginfotech.com/jdu-and-bjd-to-meet-with-opposition-in-the-context-of-gst</t>
   </si>
 </sst>
 </file>
@@ -504,7 +627,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -517,6 +640,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -580,8 +706,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{2DB3396E-FD0B-4F9C-842A-9832690A92E5}" name="Table2" displayName="Table2" ref="A1:L13" totalsRowShown="0" headerRowDxfId="13" dataDxfId="12">
-  <autoFilter ref="A1:L13" xr:uid="{2DB3396E-FD0B-4F9C-842A-9832690A92E5}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{2DB3396E-FD0B-4F9C-842A-9832690A92E5}" name="Table2" displayName="Table2" ref="A1:L17" totalsRowShown="0" headerRowDxfId="13" dataDxfId="12">
+  <autoFilter ref="A1:L17" xr:uid="{2DB3396E-FD0B-4F9C-842A-9832690A92E5}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:L11">
     <sortCondition ref="A1:A11"/>
   </sortState>
@@ -889,7 +1015,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4B667CDE-8E2B-439F-AECC-B04A1264504F}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:L13"/>
+  <dimension ref="A1:L23"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="1"/>
@@ -1389,6 +1515,151 @@
         <v>139</v>
       </c>
       <c r="L13" s="2"/>
+    </row>
+    <row r="14" spans="1:12" ht="409.5" x14ac:dyDescent="0.25">
+      <c r="A14" s="2">
+        <v>2023</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="K14" s="2"/>
+      <c r="L14" s="2"/>
+    </row>
+    <row r="15" spans="1:12" ht="409.5" x14ac:dyDescent="0.25">
+      <c r="A15" s="2">
+        <v>2023</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="G15" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="I15" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="J15" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="K15" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="L15" s="3" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" ht="409.5" x14ac:dyDescent="0.25">
+      <c r="A16" s="2">
+        <v>2015</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="G16" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="I16" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="J16" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="K16" s="2"/>
+      <c r="L16" s="2"/>
+    </row>
+    <row r="17" spans="1:12" ht="409.5" x14ac:dyDescent="0.25">
+      <c r="A17" s="2">
+        <v>2016</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="F17" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="G17" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="H17" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="I17" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="J17" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="K17" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="L17" s="2"/>
+    </row>
+    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="J23" s="5"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -1436,10 +1707,21 @@
     <hyperlink ref="I13" r:id="rId42" xr:uid="{F201AD63-64AB-4E23-B1A2-A754D95D05BB}"/>
     <hyperlink ref="J13" r:id="rId43" xr:uid="{C5EB7AEA-82C5-46D6-A06A-72D974C5ACD3}"/>
     <hyperlink ref="K13" r:id="rId44" xr:uid="{0247CA60-0A5B-4BF2-9011-61F24CD43C64}"/>
+    <hyperlink ref="J14" r:id="rId45" xr:uid="{3CAD5311-82C9-4CA1-BDDF-D0A51FC18B7D}"/>
+    <hyperlink ref="I14" r:id="rId46" xr:uid="{3D4B5B9D-E784-4F21-B75F-1E9B69F37B40}"/>
+    <hyperlink ref="J15" r:id="rId47" xr:uid="{583131D7-EDBC-4897-A4CF-42C216FF7C11}"/>
+    <hyperlink ref="L15" r:id="rId48" xr:uid="{89047251-A9F8-43FC-A50E-A9E0844B3D10}"/>
+    <hyperlink ref="K15" r:id="rId49" xr:uid="{C2DAC465-7EE8-4D06-9C55-A25E4013120E}"/>
+    <hyperlink ref="I15" r:id="rId50" xr:uid="{F97D2567-74A4-4BC8-B46D-5C5B6307FC09}"/>
+    <hyperlink ref="I16" r:id="rId51" xr:uid="{E776DED5-7F8B-41F3-8C5D-D2A53DDBCE78}"/>
+    <hyperlink ref="J16" r:id="rId52" xr:uid="{EBD5B9C3-E645-4703-B533-0D85B7DFF3BF}"/>
+    <hyperlink ref="J17" r:id="rId53" xr:uid="{EB078C19-3018-4550-9C59-85D34E4148C9}"/>
+    <hyperlink ref="I17" r:id="rId54" xr:uid="{DC66DC22-E313-4E3D-9D2B-4A8322DEFFE3}"/>
+    <hyperlink ref="K17" r:id="rId55" xr:uid="{578E13CB-736D-4F21-9BB4-A8A0FB3034E1}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
-    <tablePart r:id="rId45"/>
+    <tablePart r:id="rId56"/>
   </tableParts>
 </worksheet>
 </file>